--- a/AAII_Financials/Yearly/LFT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/LFT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="92">
   <si>
     <t>LFT</t>
   </si>
@@ -3807,8 +3807,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-700</v>
+      <c r="D91" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E91" s="3" t="s">
         <v>8</v>
